--- a/final/leaderboard.xlsx
+++ b/final/leaderboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meInspiron\Desktop\IPL Polls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meInspiron\Desktop\ipl_polls\final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9246889-67F9-4C30-81AF-B6A9B607FB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE176C2E-E124-4084-8617-41A9EEB5B04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{33315BC7-FE13-4B47-AD11-5FFBB64D564A}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Week1!$D$5:$O$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Week2!$D$5:$O$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Week2!$B$5:$V$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="188">
   <si>
     <t>Username</t>
   </si>
@@ -494,16 +494,10 @@
     <t>Match #19</t>
   </si>
   <si>
-    <t>Match #20</t>
-  </si>
-  <si>
     <t>PBKS vs RR</t>
   </si>
   <si>
     <t>SRH vs GT</t>
-  </si>
-  <si>
-    <t>MI vs RCB</t>
   </si>
   <si>
     <t>Week1</t>
@@ -685,7 +679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -998,11 +992,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1048,6 +1081,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1100,6 +1145,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1118,373 +1169,19 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEBF3FB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEBF3FB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEBF3FB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1586,119 +1283,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFEBF3FB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1783,59 +1370,16 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFEBF3FB"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor rgb="FFEBF3FB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2185,1260 +1729,1260 @@
   <sheetData>
     <row r="1" spans="2:6" ht="5.25" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:6" ht="14.25" customHeight="1">
-      <c r="B2" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="48" t="s">
+      <c r="B2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="49" t="s">
         <v>154</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>155</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="14.25" customHeight="1">
       <c r="B3" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="43">
+        <v>49</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="20">
         <v>5</v>
       </c>
-      <c r="E3" s="43">
-        <v>2</v>
-      </c>
-      <c r="F3" s="9">
+      <c r="E3" s="20">
         <v>7</v>
+      </c>
+      <c r="F3" s="20">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="14.25" customHeight="1">
       <c r="B4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="43">
-        <v>3</v>
-      </c>
-      <c r="E4" s="43">
+      <c r="D4" s="20">
         <v>4</v>
       </c>
-      <c r="F4" s="9">
-        <v>7</v>
+      <c r="E4" s="20">
+        <v>6</v>
+      </c>
+      <c r="F4" s="20">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="43">
-        <v>3</v>
-      </c>
-      <c r="E5" s="43">
-        <v>3</v>
-      </c>
-      <c r="F5" s="9">
-        <v>6</v>
+        <v>107</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="20">
+        <v>7</v>
+      </c>
+      <c r="E5" s="20">
+        <v>2</v>
+      </c>
+      <c r="F5" s="20">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="43">
+        <v>75</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="20">
         <v>4</v>
       </c>
-      <c r="E6" s="43">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="E6" s="20">
         <v>5</v>
+      </c>
+      <c r="F6" s="20">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="43">
+        <v>54</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="20">
         <v>3</v>
       </c>
-      <c r="E7" s="43">
-        <v>2</v>
-      </c>
-      <c r="F7" s="9">
-        <v>5</v>
+      <c r="E7" s="20">
+        <v>6</v>
+      </c>
+      <c r="F7" s="20">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="20">
         <v>3</v>
       </c>
-      <c r="E8" s="43">
-        <v>2</v>
-      </c>
-      <c r="F8" s="9">
-        <v>5</v>
+      <c r="E8" s="20">
+        <v>6</v>
+      </c>
+      <c r="F8" s="20">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="43">
+        <v>105</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="20">
         <v>3</v>
       </c>
-      <c r="E9" s="43">
-        <v>1</v>
-      </c>
-      <c r="F9" s="9">
-        <v>4</v>
+      <c r="E9" s="20">
+        <v>6</v>
+      </c>
+      <c r="F9" s="20">
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:6">
       <c r="B10" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="43">
-        <v>3</v>
-      </c>
-      <c r="E10" s="43">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9">
-        <v>4</v>
+        <v>63</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="20">
+        <v>2</v>
+      </c>
+      <c r="E10" s="20">
+        <v>7</v>
+      </c>
+      <c r="F10" s="20">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="43">
-        <v>3</v>
-      </c>
-      <c r="E11" s="43">
-        <v>1</v>
-      </c>
-      <c r="F11" s="9">
+        <v>33</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="20">
         <v>4</v>
+      </c>
+      <c r="E11" s="20">
+        <v>4</v>
+      </c>
+      <c r="F11" s="20">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="43">
-        <v>2</v>
-      </c>
-      <c r="E12" s="43">
-        <v>2</v>
-      </c>
-      <c r="F12" s="9">
-        <v>4</v>
+        <v>65</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="20">
+        <v>3</v>
+      </c>
+      <c r="E12" s="20">
+        <v>5</v>
+      </c>
+      <c r="F12" s="20">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="14.25" customHeight="1">
       <c r="B13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="43">
-        <v>2</v>
-      </c>
-      <c r="E13" s="43">
-        <v>2</v>
-      </c>
-      <c r="F13" s="9">
-        <v>4</v>
+        <v>77</v>
+      </c>
+      <c r="C13" s="51"/>
+      <c r="D13" s="20">
+        <v>2</v>
+      </c>
+      <c r="E13" s="20">
+        <v>6</v>
+      </c>
+      <c r="F13" s="20">
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="14.25" customHeight="1">
       <c r="B14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="43">
-        <v>2</v>
-      </c>
-      <c r="E14" s="43">
-        <v>2</v>
-      </c>
-      <c r="F14" s="9">
-        <v>4</v>
+        <v>122</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="20">
+        <v>2</v>
+      </c>
+      <c r="E14" s="20">
+        <v>6</v>
+      </c>
+      <c r="F14" s="20">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="14.25" customHeight="1">
       <c r="B15" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="43">
-        <v>2</v>
-      </c>
-      <c r="E15" s="43">
-        <v>2</v>
-      </c>
-      <c r="F15" s="9">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="20">
+        <v>1</v>
+      </c>
+      <c r="E15" s="20">
+        <v>7</v>
+      </c>
+      <c r="F15" s="20">
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="14.25" customHeight="1">
       <c r="B16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="43">
-        <v>2</v>
-      </c>
-      <c r="E16" s="43">
-        <v>2</v>
-      </c>
-      <c r="F16" s="9">
-        <v>4</v>
+        <v>56</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="20">
+        <v>6</v>
+      </c>
+      <c r="E16" s="20">
+        <v>1</v>
+      </c>
+      <c r="F16" s="20">
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" s="43">
-        <v>2</v>
-      </c>
-      <c r="E17" s="43">
-        <v>2</v>
-      </c>
-      <c r="F17" s="9">
+        <v>32</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="20">
+        <v>3</v>
+      </c>
+      <c r="E17" s="20">
         <v>4</v>
+      </c>
+      <c r="F17" s="20">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="43">
-        <v>1</v>
-      </c>
-      <c r="E18" s="43">
+        <v>45</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="20">
         <v>3</v>
       </c>
-      <c r="F18" s="9">
+      <c r="E18" s="20">
         <v>4</v>
+      </c>
+      <c r="F18" s="20">
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="43">
-        <v>1</v>
-      </c>
-      <c r="E19" s="43">
-        <v>3</v>
-      </c>
-      <c r="F19" s="9">
-        <v>4</v>
+        <v>80</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="20">
+        <v>2</v>
+      </c>
+      <c r="E19" s="20">
+        <v>5</v>
+      </c>
+      <c r="F19" s="20">
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="43">
-        <v>1</v>
-      </c>
-      <c r="E20" s="43">
-        <v>3</v>
-      </c>
-      <c r="F20" s="9">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="20">
+        <v>0</v>
+      </c>
+      <c r="E20" s="20">
+        <v>7</v>
+      </c>
+      <c r="F20" s="20">
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="43">
-        <v>2</v>
-      </c>
-      <c r="E21" s="43">
-        <v>1</v>
-      </c>
-      <c r="F21" s="9">
+        <v>99</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="20">
         <v>3</v>
+      </c>
+      <c r="E21" s="20">
+        <v>3</v>
+      </c>
+      <c r="F21" s="20">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="43">
-        <v>2</v>
-      </c>
-      <c r="E22" s="43">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="20">
+        <v>0</v>
+      </c>
+      <c r="E22" s="20">
+        <v>6</v>
+      </c>
+      <c r="F22" s="20">
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="43">
-        <v>1</v>
-      </c>
-      <c r="E23" s="43">
-        <v>2</v>
-      </c>
-      <c r="F23" s="9">
-        <v>3</v>
+        <v>124</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="20">
+        <v>0</v>
+      </c>
+      <c r="E23" s="20">
+        <v>6</v>
+      </c>
+      <c r="F23" s="20">
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="43">
-        <v>1</v>
-      </c>
-      <c r="E24" s="43">
-        <v>2</v>
-      </c>
-      <c r="F24" s="9">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="20">
+        <v>4</v>
+      </c>
+      <c r="E24" s="20">
+        <v>1</v>
+      </c>
+      <c r="F24" s="20">
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="43">
-        <v>1</v>
-      </c>
-      <c r="E25" s="43">
-        <v>2</v>
-      </c>
-      <c r="F25" s="9">
-        <v>3</v>
+        <v>38</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="20">
+        <v>1</v>
+      </c>
+      <c r="E25" s="20">
+        <v>4</v>
+      </c>
+      <c r="F25" s="20">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="43">
-        <v>1</v>
-      </c>
-      <c r="E26" s="43">
-        <v>2</v>
-      </c>
-      <c r="F26" s="9">
-        <v>3</v>
+        <v>89</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="20">
+        <v>1</v>
+      </c>
+      <c r="E26" s="20">
+        <v>4</v>
+      </c>
+      <c r="F26" s="20">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="43">
-        <v>0</v>
-      </c>
-      <c r="E27" s="43">
-        <v>3</v>
-      </c>
-      <c r="F27" s="9">
-        <v>3</v>
+        <v>117</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="20">
+        <v>1</v>
+      </c>
+      <c r="E27" s="20">
+        <v>4</v>
+      </c>
+      <c r="F27" s="20">
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" s="43">
-        <v>2</v>
-      </c>
-      <c r="E28" s="43">
-        <v>0</v>
-      </c>
-      <c r="F28" s="9">
-        <v>2</v>
+        <v>78</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="20">
+        <v>3</v>
+      </c>
+      <c r="E28" s="20">
+        <v>1</v>
+      </c>
+      <c r="F28" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="43">
-        <v>2</v>
-      </c>
-      <c r="E29" s="43">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9">
-        <v>2</v>
+        <v>113</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="20">
+        <v>2</v>
+      </c>
+      <c r="E29" s="20">
+        <v>2</v>
+      </c>
+      <c r="F29" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="43">
-        <v>2</v>
-      </c>
-      <c r="E30" s="43">
-        <v>0</v>
-      </c>
-      <c r="F30" s="9">
-        <v>2</v>
+        <v>71</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="20">
+        <v>1</v>
+      </c>
+      <c r="E30" s="20">
+        <v>3</v>
+      </c>
+      <c r="F30" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="43">
-        <v>2</v>
-      </c>
-      <c r="E31" s="43">
-        <v>0</v>
-      </c>
-      <c r="F31" s="9">
-        <v>2</v>
+        <v>95</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="20">
+        <v>1</v>
+      </c>
+      <c r="E31" s="20">
+        <v>3</v>
+      </c>
+      <c r="F31" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="43">
-        <v>2</v>
-      </c>
-      <c r="E32" s="43">
-        <v>0</v>
-      </c>
-      <c r="F32" s="9">
-        <v>2</v>
+        <v>36</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="20">
+        <v>0</v>
+      </c>
+      <c r="E32" s="20">
+        <v>4</v>
+      </c>
+      <c r="F32" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="43">
-        <v>1</v>
-      </c>
-      <c r="E33" s="43">
-        <v>1</v>
-      </c>
-      <c r="F33" s="9">
-        <v>2</v>
+        <v>91</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="20">
+        <v>0</v>
+      </c>
+      <c r="E33" s="20">
+        <v>4</v>
+      </c>
+      <c r="F33" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="43">
-        <v>1</v>
-      </c>
-      <c r="E34" s="43">
-        <v>1</v>
-      </c>
-      <c r="F34" s="9">
-        <v>2</v>
+        <v>183</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="20">
+        <v>0</v>
+      </c>
+      <c r="E34" s="20">
+        <v>4</v>
+      </c>
+      <c r="F34" s="20">
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D35" s="43">
-        <v>1</v>
-      </c>
-      <c r="E35" s="43">
-        <v>1</v>
-      </c>
-      <c r="F35" s="9">
-        <v>2</v>
+        <v>43</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="20">
+        <v>1</v>
+      </c>
+      <c r="E35" s="20">
+        <v>2</v>
+      </c>
+      <c r="F35" s="20">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="43">
-        <v>0</v>
-      </c>
-      <c r="E36" s="43">
-        <v>2</v>
-      </c>
-      <c r="F36" s="9">
-        <v>2</v>
+        <v>93</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="20">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20">
+        <v>3</v>
+      </c>
+      <c r="F36" s="20">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D37" s="43">
-        <v>0</v>
-      </c>
-      <c r="E37" s="43">
-        <v>2</v>
-      </c>
-      <c r="F37" s="9">
-        <v>2</v>
+        <v>157</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
+        <v>3</v>
+      </c>
+      <c r="F37" s="20">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="43">
-        <v>0</v>
-      </c>
-      <c r="E38" s="43">
-        <v>2</v>
-      </c>
-      <c r="F38" s="9">
-        <v>2</v>
+        <v>165</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38" s="20">
+        <v>0</v>
+      </c>
+      <c r="E38" s="20">
+        <v>3</v>
+      </c>
+      <c r="F38" s="20">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" s="43">
-        <v>0</v>
-      </c>
-      <c r="E39" s="43">
-        <v>2</v>
-      </c>
-      <c r="F39" s="9">
+        <v>85</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="20">
+        <v>2</v>
+      </c>
+      <c r="E39" s="20">
+        <v>0</v>
+      </c>
+      <c r="F39" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D40" s="43">
-        <v>0</v>
-      </c>
-      <c r="E40" s="43">
-        <v>2</v>
-      </c>
-      <c r="F40" s="9">
+        <v>111</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="20">
+        <v>2</v>
+      </c>
+      <c r="E40" s="20">
+        <v>0</v>
+      </c>
+      <c r="F40" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" s="43">
-        <v>1</v>
-      </c>
-      <c r="E41" s="43">
-        <v>0</v>
-      </c>
-      <c r="F41" s="9">
-        <v>1</v>
+        <v>83</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="20">
+        <v>2</v>
+      </c>
+      <c r="E41" s="20">
+        <v>0</v>
+      </c>
+      <c r="F41" s="20">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="43">
-        <v>1</v>
-      </c>
-      <c r="E42" s="43">
-        <v>0</v>
-      </c>
-      <c r="F42" s="9">
-        <v>1</v>
+        <v>101</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="20">
+        <v>2</v>
+      </c>
+      <c r="E42" s="20">
+        <v>0</v>
+      </c>
+      <c r="F42" s="20">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" s="43">
-        <v>1</v>
-      </c>
-      <c r="E43" s="43">
-        <v>0</v>
-      </c>
-      <c r="F43" s="9">
-        <v>1</v>
+        <v>130</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="20">
+        <v>2</v>
+      </c>
+      <c r="E43" s="20">
+        <v>0</v>
+      </c>
+      <c r="F43" s="20">
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" s="43">
-        <v>1</v>
-      </c>
-      <c r="E44" s="43">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9">
-        <v>1</v>
+        <v>42</v>
+      </c>
+      <c r="C44" s="51"/>
+      <c r="D44" s="20">
+        <v>1</v>
+      </c>
+      <c r="E44" s="20">
+        <v>1</v>
+      </c>
+      <c r="F44" s="20">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="43">
-        <v>1</v>
-      </c>
-      <c r="E45" s="43">
-        <v>0</v>
-      </c>
-      <c r="F45" s="9">
-        <v>1</v>
+        <v>155</v>
+      </c>
+      <c r="C45" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" s="20">
+        <v>0</v>
+      </c>
+      <c r="E45" s="20">
+        <v>2</v>
+      </c>
+      <c r="F45" s="20">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="43">
-        <v>1</v>
-      </c>
-      <c r="E46" s="43">
-        <v>0</v>
-      </c>
-      <c r="F46" s="9">
+        <v>24</v>
+      </c>
+      <c r="C46" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="20">
+        <v>1</v>
+      </c>
+      <c r="E46" s="20">
+        <v>0</v>
+      </c>
+      <c r="F46" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" s="43">
-        <v>1</v>
-      </c>
-      <c r="E47" s="43">
-        <v>0</v>
-      </c>
-      <c r="F47" s="9">
+        <v>26</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="20">
+        <v>1</v>
+      </c>
+      <c r="E47" s="20">
+        <v>0</v>
+      </c>
+      <c r="F47" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D48" s="43">
-        <v>1</v>
-      </c>
-      <c r="E48" s="43">
-        <v>0</v>
-      </c>
-      <c r="F48" s="9">
+        <v>40</v>
+      </c>
+      <c r="C48" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="20">
+        <v>1</v>
+      </c>
+      <c r="E48" s="20">
+        <v>0</v>
+      </c>
+      <c r="F48" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D49" s="43">
-        <v>1</v>
-      </c>
-      <c r="E49" s="43">
-        <v>0</v>
-      </c>
-      <c r="F49" s="9">
+        <v>47</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="20">
+        <v>1</v>
+      </c>
+      <c r="E49" s="20">
+        <v>0</v>
+      </c>
+      <c r="F49" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" s="43">
-        <v>0</v>
-      </c>
-      <c r="E50" s="43">
-        <v>1</v>
-      </c>
-      <c r="F50" s="9">
+        <v>51</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="20">
+        <v>1</v>
+      </c>
+      <c r="E50" s="20">
+        <v>0</v>
+      </c>
+      <c r="F50" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D51" s="43">
-        <v>0</v>
-      </c>
-      <c r="E51" s="43">
-        <v>1</v>
-      </c>
-      <c r="F51" s="9">
+        <v>67</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="20">
+        <v>1</v>
+      </c>
+      <c r="E51" s="20">
+        <v>0</v>
+      </c>
+      <c r="F51" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D52" s="43">
-        <v>0</v>
-      </c>
-      <c r="E52" s="43">
-        <v>1</v>
-      </c>
-      <c r="F52" s="9">
+        <v>103</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" s="20">
+        <v>1</v>
+      </c>
+      <c r="E52" s="20">
+        <v>0</v>
+      </c>
+      <c r="F52" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="D53" s="43">
-        <v>0</v>
-      </c>
-      <c r="E53" s="43">
-        <v>1</v>
-      </c>
-      <c r="F53" s="9">
+        <v>120</v>
+      </c>
+      <c r="C53" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="D53" s="20">
+        <v>1</v>
+      </c>
+      <c r="E53" s="20">
+        <v>0</v>
+      </c>
+      <c r="F53" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D54" s="43">
-        <v>0</v>
-      </c>
-      <c r="E54" s="43">
-        <v>1</v>
-      </c>
-      <c r="F54" s="9">
+        <v>159</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" s="20">
+        <v>0</v>
+      </c>
+      <c r="E54" s="20">
+        <v>1</v>
+      </c>
+      <c r="F54" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D55" s="43">
-        <v>0</v>
-      </c>
-      <c r="E55" s="43">
-        <v>1</v>
-      </c>
-      <c r="F55" s="9">
+        <v>161</v>
+      </c>
+      <c r="C55" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="D55" s="20">
+        <v>0</v>
+      </c>
+      <c r="E55" s="20">
+        <v>1</v>
+      </c>
+      <c r="F55" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D56" s="43">
-        <v>0</v>
-      </c>
-      <c r="E56" s="43">
-        <v>1</v>
-      </c>
-      <c r="F56" s="9">
+        <v>163</v>
+      </c>
+      <c r="C56" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="D56" s="20">
+        <v>0</v>
+      </c>
+      <c r="E56" s="20">
+        <v>1</v>
+      </c>
+      <c r="F56" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D57" s="43">
-        <v>0</v>
-      </c>
-      <c r="E57" s="43">
-        <v>1</v>
-      </c>
-      <c r="F57" s="9">
+        <v>167</v>
+      </c>
+      <c r="C57" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57" s="20">
+        <v>0</v>
+      </c>
+      <c r="E57" s="20">
+        <v>1</v>
+      </c>
+      <c r="F57" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D58" s="43">
-        <v>0</v>
-      </c>
-      <c r="E58" s="43">
-        <v>0</v>
-      </c>
-      <c r="F58" s="9">
-        <v>0</v>
+        <v>169</v>
+      </c>
+      <c r="C58" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D58" s="20">
+        <v>0</v>
+      </c>
+      <c r="E58" s="20">
+        <v>1</v>
+      </c>
+      <c r="F58" s="20">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" s="43">
-        <v>0</v>
-      </c>
-      <c r="E59" s="43">
-        <v>0</v>
-      </c>
-      <c r="F59" s="9">
+        <v>19</v>
+      </c>
+      <c r="C59" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="20">
+        <v>0</v>
+      </c>
+      <c r="E59" s="20">
+        <v>0</v>
+      </c>
+      <c r="F59" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D60" s="43">
-        <v>0</v>
-      </c>
-      <c r="E60" s="43">
-        <v>0</v>
-      </c>
-      <c r="F60" s="9">
+        <v>22</v>
+      </c>
+      <c r="C60" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="20">
+        <v>0</v>
+      </c>
+      <c r="E60" s="20">
+        <v>0</v>
+      </c>
+      <c r="F60" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="43">
-        <v>0</v>
-      </c>
-      <c r="E61" s="43">
-        <v>0</v>
-      </c>
-      <c r="F61" s="9">
+        <v>35</v>
+      </c>
+      <c r="C61" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="20">
+        <v>0</v>
+      </c>
+      <c r="E61" s="20">
+        <v>0</v>
+      </c>
+      <c r="F61" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" s="43">
-        <v>0</v>
-      </c>
-      <c r="E62" s="43">
-        <v>0</v>
-      </c>
-      <c r="F62" s="9">
+        <v>53</v>
+      </c>
+      <c r="C62" s="51"/>
+      <c r="D62" s="20">
+        <v>0</v>
+      </c>
+      <c r="E62" s="20">
+        <v>0</v>
+      </c>
+      <c r="F62" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D63" s="43">
-        <v>0</v>
-      </c>
-      <c r="E63" s="43">
-        <v>0</v>
-      </c>
-      <c r="F63" s="9">
+        <v>58</v>
+      </c>
+      <c r="C63" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" s="20">
+        <v>0</v>
+      </c>
+      <c r="E63" s="20">
+        <v>0</v>
+      </c>
+      <c r="F63" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D64" s="43">
-        <v>0</v>
-      </c>
-      <c r="E64" s="43">
-        <v>0</v>
-      </c>
-      <c r="F64" s="9">
+        <v>62</v>
+      </c>
+      <c r="C64" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="D64" s="20">
+        <v>0</v>
+      </c>
+      <c r="E64" s="20">
+        <v>0</v>
+      </c>
+      <c r="F64" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D65" s="43">
-        <v>0</v>
-      </c>
-      <c r="E65" s="43">
-        <v>0</v>
-      </c>
-      <c r="F65" s="9">
+        <v>109</v>
+      </c>
+      <c r="C65" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="D65" s="20">
+        <v>0</v>
+      </c>
+      <c r="E65" s="20">
+        <v>0</v>
+      </c>
+      <c r="F65" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D66" s="43">
-        <v>0</v>
-      </c>
-      <c r="E66" s="43">
-        <v>0</v>
-      </c>
-      <c r="F66" s="9">
+        <v>118</v>
+      </c>
+      <c r="C66" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" s="20">
+        <v>0</v>
+      </c>
+      <c r="E66" s="20">
+        <v>0</v>
+      </c>
+      <c r="F66" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D67" s="43">
-        <v>0</v>
-      </c>
-      <c r="E67" s="43">
-        <v>0</v>
-      </c>
-      <c r="F67" s="9">
+        <v>115</v>
+      </c>
+      <c r="C67" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D67" s="20">
+        <v>0</v>
+      </c>
+      <c r="E67" s="20">
+        <v>0</v>
+      </c>
+      <c r="F67" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D68" s="43">
-        <v>0</v>
-      </c>
-      <c r="E68" s="43">
-        <v>0</v>
-      </c>
-      <c r="F68" s="9">
+        <v>132</v>
+      </c>
+      <c r="C68" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="20">
+        <v>0</v>
+      </c>
+      <c r="E68" s="20">
+        <v>0</v>
+      </c>
+      <c r="F68" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D69" s="43">
-        <v>0</v>
-      </c>
-      <c r="E69" s="43">
-        <v>0</v>
-      </c>
-      <c r="F69" s="9">
+        <v>171</v>
+      </c>
+      <c r="C69" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="D69" s="20">
+        <v>0</v>
+      </c>
+      <c r="E69" s="20">
+        <v>0</v>
+      </c>
+      <c r="F69" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D70" s="43">
-        <v>0</v>
-      </c>
-      <c r="E70" s="43">
-        <v>0</v>
-      </c>
-      <c r="F70" s="9">
+        <v>173</v>
+      </c>
+      <c r="C70" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="D70" s="20">
+        <v>0</v>
+      </c>
+      <c r="E70" s="20">
+        <v>0</v>
+      </c>
+      <c r="F70" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="D71" s="43">
-        <v>0</v>
-      </c>
-      <c r="E71" s="43">
-        <v>0</v>
-      </c>
-      <c r="F71" s="9">
+        <v>175</v>
+      </c>
+      <c r="C71" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="D71" s="20">
+        <v>0</v>
+      </c>
+      <c r="E71" s="20">
+        <v>0</v>
+      </c>
+      <c r="F71" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D72" s="43">
-        <v>0</v>
-      </c>
-      <c r="E72" s="43">
-        <v>0</v>
-      </c>
-      <c r="F72" s="9">
+        <v>177</v>
+      </c>
+      <c r="C72" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="D72" s="20">
+        <v>0</v>
+      </c>
+      <c r="E72" s="20">
+        <v>0</v>
+      </c>
+      <c r="F72" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D73" s="43">
-        <v>0</v>
-      </c>
-      <c r="E73" s="43">
-        <v>0</v>
-      </c>
-      <c r="F73" s="9">
+        <v>179</v>
+      </c>
+      <c r="C73" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="D73" s="20">
+        <v>0</v>
+      </c>
+      <c r="E73" s="20">
+        <v>0</v>
+      </c>
+      <c r="F73" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D74" s="43">
-        <v>0</v>
-      </c>
-      <c r="E74" s="43">
-        <v>0</v>
-      </c>
-      <c r="F74" s="9">
+        <v>181</v>
+      </c>
+      <c r="C74" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="D74" s="20">
+        <v>0</v>
+      </c>
+      <c r="E74" s="20">
+        <v>0</v>
+      </c>
+      <c r="F74" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" thickBot="1">
       <c r="B75" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D75" s="44">
-        <v>0</v>
-      </c>
-      <c r="E75" s="44">
-        <v>0</v>
-      </c>
-      <c r="F75" s="10">
+        <v>185</v>
+      </c>
+      <c r="C75" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="D75" s="21">
+        <v>0</v>
+      </c>
+      <c r="E75" s="21">
+        <v>0</v>
+      </c>
+      <c r="F75" s="21">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:F200">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3471,121 +3015,121 @@
   <sheetData>
     <row r="1" spans="2:18" ht="5.25" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="30"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="34"/>
     </row>
     <row r="3" spans="2:18" ht="15">
-      <c r="B3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="36"/>
+      <c r="F3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="36"/>
+      <c r="H3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="31" t="s">
+      <c r="I3" s="36"/>
+      <c r="J3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="31" t="s">
+      <c r="K3" s="36"/>
+      <c r="L3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="32"/>
-      <c r="N3" s="31" t="s">
+      <c r="M3" s="36"/>
+      <c r="N3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="26" t="s">
+      <c r="O3" s="36"/>
+      <c r="P3" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="49" t="s">
-        <v>189</v>
+      <c r="R3" s="41" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="15">
-      <c r="B4" s="21"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="33" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="33" t="s">
+      <c r="E4" s="38"/>
+      <c r="F4" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="33" t="s">
+      <c r="G4" s="38"/>
+      <c r="H4" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="34"/>
-      <c r="J4" s="33" t="s">
+      <c r="I4" s="38"/>
+      <c r="J4" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="34"/>
-      <c r="L4" s="33" t="s">
+      <c r="K4" s="38"/>
+      <c r="L4" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="34"/>
-      <c r="N4" s="33" t="s">
+      <c r="M4" s="38"/>
+      <c r="N4" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="34"/>
-      <c r="P4" s="26"/>
-      <c r="R4" s="50"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="30"/>
+      <c r="R4" s="42"/>
     </row>
     <row r="5" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B5" s="22"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="35" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="35" t="s">
+      <c r="E5" s="40"/>
+      <c r="F5" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="35" t="s">
+      <c r="G5" s="40"/>
+      <c r="H5" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="36"/>
-      <c r="J5" s="35" t="s">
+      <c r="I5" s="40"/>
+      <c r="J5" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="36"/>
-      <c r="L5" s="35" t="s">
+      <c r="K5" s="40"/>
+      <c r="L5" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="M5" s="36"/>
-      <c r="N5" s="35" t="s">
+      <c r="M5" s="40"/>
+      <c r="N5" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="36"/>
-      <c r="P5" s="27"/>
-      <c r="R5" s="50"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="31"/>
+      <c r="R5" s="42"/>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" s="14" t="s">
@@ -3634,7 +3178,7 @@
         <f t="shared" ref="P6:P37" si="0">SUM(D6:O6)</f>
         <v>7</v>
       </c>
-      <c r="R6" s="43">
+      <c r="R6" s="20">
         <f>COUNTIF(D6:O6,"---")</f>
         <v>1</v>
       </c>
@@ -3686,7 +3230,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="R7" s="43">
+      <c r="R7" s="20">
         <f>COUNTIF(D7:O7,"---")</f>
         <v>0</v>
       </c>
@@ -3738,7 +3282,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="R8" s="43">
+      <c r="R8" s="20">
         <f t="shared" ref="R8:R62" si="1">COUNTIF(D8:O8,"---")</f>
         <v>0</v>
       </c>
@@ -3790,7 +3334,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="R9" s="43">
+      <c r="R9" s="20">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -3842,7 +3386,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="R10" s="43">
+      <c r="R10" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3894,7 +3438,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="R11" s="43">
+      <c r="R11" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3946,7 +3490,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="R12" s="43">
+      <c r="R12" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3998,7 +3542,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R13" s="43">
+      <c r="R13" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4050,7 +3594,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R14" s="43">
+      <c r="R14" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4102,7 +3646,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R15" s="43">
+      <c r="R15" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -4154,7 +3698,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R16" s="43">
+      <c r="R16" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -4206,7 +3750,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R17" s="43">
+      <c r="R17" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -4258,7 +3802,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R18" s="43">
+      <c r="R18" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4310,7 +3854,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R19" s="43">
+      <c r="R19" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4362,7 +3906,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R20" s="43">
+      <c r="R20" s="20">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -4414,7 +3958,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R21" s="43">
+      <c r="R21" s="20">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -4466,7 +4010,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R22" s="43">
+      <c r="R22" s="20">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -4518,7 +4062,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R23" s="43">
+      <c r="R23" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -4570,7 +4114,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R24" s="43">
+      <c r="R24" s="20">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -4622,7 +4166,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R25" s="43">
+      <c r="R25" s="20">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -4674,7 +4218,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R26" s="43">
+      <c r="R26" s="20">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -4726,7 +4270,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R27" s="43">
+      <c r="R27" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -4778,7 +4322,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R28" s="43">
+      <c r="R28" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -4828,7 +4372,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R29" s="43">
+      <c r="R29" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4880,7 +4424,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R30" s="43">
+      <c r="R30" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4932,7 +4476,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R31" s="43">
+      <c r="R31" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -4984,7 +4528,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R32" s="43">
+      <c r="R32" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5036,7 +4580,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R33" s="43">
+      <c r="R33" s="20">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -5088,7 +4632,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R34" s="43">
+      <c r="R34" s="20">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -5140,7 +4684,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R35" s="43">
+      <c r="R35" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5190,7 +4734,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R36" s="43">
+      <c r="R36" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -5242,7 +4786,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R37" s="43">
+      <c r="R37" s="20">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -5294,7 +4838,7 @@
         <f t="shared" ref="P38:P62" si="2">SUM(D38:O38)</f>
         <v>1</v>
       </c>
-      <c r="R38" s="43">
+      <c r="R38" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5346,7 +4890,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R39" s="43">
+      <c r="R39" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -5398,7 +4942,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R40" s="43">
+      <c r="R40" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5450,7 +4994,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R41" s="43">
+      <c r="R41" s="20">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5502,7 +5046,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R42" s="43">
+      <c r="R42" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5554,7 +5098,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R43" s="43">
+      <c r="R43" s="20">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -5606,7 +5150,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R44" s="43">
+      <c r="R44" s="20">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -5658,7 +5202,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R45" s="43">
+      <c r="R45" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5710,7 +5254,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R46" s="43">
+      <c r="R46" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5762,7 +5306,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R47" s="43">
+      <c r="R47" s="20">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5814,7 +5358,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R48" s="43">
+      <c r="R48" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5866,7 +5410,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R49" s="43">
+      <c r="R49" s="20">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -5918,7 +5462,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R50" s="43">
+      <c r="R50" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5970,7 +5514,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R51" s="43">
+      <c r="R51" s="20">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6022,7 +5566,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R52" s="43">
+      <c r="R52" s="20">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -6074,7 +5618,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R53" s="43">
+      <c r="R53" s="20">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -6126,7 +5670,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R54" s="43">
+      <c r="R54" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -6176,7 +5720,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R55" s="43">
+      <c r="R55" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -6228,7 +5772,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R56" s="43">
+      <c r="R56" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -6280,7 +5824,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R57" s="43">
+      <c r="R57" s="20">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6332,7 +5876,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R58" s="43">
+      <c r="R58" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -6384,7 +5928,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R59" s="43">
+      <c r="R59" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -6436,7 +5980,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R60" s="43">
+      <c r="R60" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -6488,7 +6032,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R61" s="43">
+      <c r="R61" s="20">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -6540,7 +6084,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R62" s="44">
+      <c r="R62" s="21">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6574,47 +6118,47 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="J5:K5"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6:C200 P6:P200">
+    <cfRule type="expression" dxfId="19" priority="9">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="41" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
       <formula>$D$5</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576 G1:G1048576 I1:I1048576 K1:K1048576 M1:M1048576 O1:O1048576">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="cellIs" dxfId="40" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>$F$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="39" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>$H$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="cellIs" dxfId="38" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>$J$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="cellIs" dxfId="37" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>$L$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>$N$5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576 G1:G1048576 I1:I1048576 K1:K1048576 M1:M1048576 O1:O1048576">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:C200 P6:P200">
-    <cfRule type="expression" dxfId="33" priority="9">
-      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6623,7 +6167,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8B3406-738B-441F-9471-69FF55DF5805}">
-  <dimension ref="B1:X62"/>
+  <dimension ref="B1:V58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="0.625" customWidth="1"/>
@@ -6645,1877 +6189,3493 @@
     <col min="17" max="17" width="4.75" style="1" customWidth="1"/>
     <col min="18" max="18" width="11.625" style="1" customWidth="1"/>
     <col min="19" max="19" width="4.75" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="4.75" style="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" ht="5.25" customHeight="1" thickBot="1"/>
-    <row r="2" spans="2:24" ht="15.75" thickBot="1">
-      <c r="B2" s="37" t="s">
+    <row r="1" spans="2:22" ht="5.25" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:22" ht="15.75" thickBot="1">
+      <c r="B2" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="39"/>
-    </row>
-    <row r="3" spans="2:24" ht="15" customHeight="1">
-      <c r="B3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="31" t="s">
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="45"/>
+    </row>
+    <row r="3" spans="2:22" ht="15" customHeight="1">
+      <c r="B3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="31" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="36"/>
+      <c r="H3" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="31" t="s">
+      <c r="I3" s="36"/>
+      <c r="J3" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="31" t="s">
+      <c r="K3" s="36"/>
+      <c r="L3" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="M3" s="32"/>
-      <c r="N3" s="31" t="s">
+      <c r="M3" s="36"/>
+      <c r="N3" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="31" t="s">
+      <c r="O3" s="36"/>
+      <c r="P3" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="31" t="s">
+      <c r="Q3" s="36"/>
+      <c r="R3" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="S3" s="32"/>
-      <c r="T3" s="31" t="s">
+      <c r="S3" s="36"/>
+      <c r="T3" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" ht="15">
+      <c r="B4" s="25"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="38"/>
+      <c r="F4" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="38"/>
+      <c r="H4" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I4" s="38"/>
+      <c r="J4" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="L4" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="M4" s="38"/>
+      <c r="N4" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="O4" s="38"/>
+      <c r="P4" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="U3" s="32"/>
-      <c r="V3" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="X3" s="49" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="2:24" ht="15">
-      <c r="B4" s="21"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="I4" s="34"/>
-      <c r="J4" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="K4" s="34"/>
-      <c r="L4" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="M4" s="34"/>
-      <c r="N4" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="O4" s="34"/>
-      <c r="P4" s="33" t="s">
+      <c r="Q4" s="38"/>
+      <c r="R4" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="S4" s="34"/>
-      <c r="T4" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="U4" s="34"/>
-      <c r="V4" s="41"/>
-      <c r="X4" s="50"/>
-    </row>
-    <row r="5" spans="2:24" ht="15.75" thickBot="1">
-      <c r="B5" s="22"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="35" t="s">
+      <c r="S4" s="38"/>
+      <c r="T4" s="47"/>
+      <c r="V4" s="42"/>
+    </row>
+    <row r="5" spans="2:22" ht="15.75" thickBot="1">
+      <c r="B5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="35" t="s">
+      <c r="E5" s="40"/>
+      <c r="F5" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="35" t="s">
+      <c r="G5" s="40"/>
+      <c r="H5" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="36"/>
-      <c r="J5" s="35" t="s">
+      <c r="I5" s="40"/>
+      <c r="J5" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="36"/>
-      <c r="L5" s="35" t="s">
+      <c r="K5" s="40"/>
+      <c r="L5" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="36"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="36"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="O5" s="40"/>
+      <c r="P5" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="S5" s="40"/>
+      <c r="T5" s="48"/>
       <c r="V5" s="42"/>
-      <c r="X5" s="50"/>
-    </row>
-    <row r="6" spans="2:24">
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="19">
-        <f t="shared" ref="V6:V62" si="0">SUM(D6:O6)</f>
-        <v>0</v>
-      </c>
-      <c r="X6" s="43">
-        <f>COUNTIF(D6:U6,"---")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:24">
-      <c r="B7" s="6"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="9">
+    </row>
+    <row r="6" spans="2:22">
+      <c r="B6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="17">
+        <v>1</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="17">
+        <v>1</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="17">
+        <v>0</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="17">
+        <v>1</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="O6" s="17">
+        <v>0</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>2</v>
+      </c>
+      <c r="R6" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="S6" s="17">
+        <v>2</v>
+      </c>
+      <c r="T6" s="19">
+        <v>7</v>
+      </c>
+      <c r="V6" s="20">
+        <f t="shared" ref="V6:V37" si="0">COUNTIF(D6:S6,"---")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="B7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O7" s="3">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S7" s="3">
+        <v>2</v>
+      </c>
+      <c r="T7" s="9">
+        <v>7</v>
+      </c>
+      <c r="V7" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X7" s="43">
-        <f t="shared" ref="X7:X62" si="1">COUNTIF(D7:U7,"---")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:24">
-      <c r="B8" s="6"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="9">
+    </row>
+    <row r="8" spans="2:22">
+      <c r="B8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>2</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="9">
+        <v>7</v>
+      </c>
+      <c r="V8" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X8" s="43">
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O9" s="3">
+        <v>2</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>2</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S9" s="3">
+        <v>2</v>
+      </c>
+      <c r="T9" s="9">
+        <v>7</v>
+      </c>
+      <c r="V9" s="20">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="B10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O10" s="3">
+        <v>2</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S10" s="3">
+        <v>2</v>
+      </c>
+      <c r="T10" s="9">
+        <v>6</v>
+      </c>
+      <c r="V10" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O11" s="3">
+        <v>2</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S11" s="3">
+        <v>2</v>
+      </c>
+      <c r="T11" s="9">
+        <v>6</v>
+      </c>
+      <c r="V11" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>2</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S12" s="3">
+        <v>2</v>
+      </c>
+      <c r="T12" s="9">
+        <v>6</v>
+      </c>
+      <c r="V12" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="B13" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" s="3">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O13" s="3">
+        <v>2</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S13" s="3">
+        <v>2</v>
+      </c>
+      <c r="T13" s="9">
+        <v>6</v>
+      </c>
+      <c r="V13" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="B14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O14" s="3">
+        <v>2</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S14" s="3">
+        <v>2</v>
+      </c>
+      <c r="T14" s="9">
+        <v>6</v>
+      </c>
+      <c r="V14" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>2</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="9">
+        <v>6</v>
+      </c>
+      <c r="V15" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="B16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O16" s="3">
+        <v>2</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S16" s="3">
+        <v>2</v>
+      </c>
+      <c r="T16" s="9">
+        <v>6</v>
+      </c>
+      <c r="V16" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22">
+      <c r="B17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O17" s="3">
+        <v>2</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S17" s="3">
+        <v>2</v>
+      </c>
+      <c r="T17" s="9">
+        <v>6</v>
+      </c>
+      <c r="V17" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O18" s="3">
+        <v>2</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S18" s="3">
+        <v>2</v>
+      </c>
+      <c r="T18" s="9">
+        <v>5</v>
+      </c>
+      <c r="V18" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M19" s="3">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O19" s="3">
+        <v>2</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S19" s="3">
+        <v>2</v>
+      </c>
+      <c r="T19" s="9">
+        <v>5</v>
+      </c>
+      <c r="V19" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O20" s="3">
+        <v>2</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>2</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="9">
+        <v>5</v>
+      </c>
+      <c r="V20" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="B21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>2</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="9">
+        <v>4</v>
+      </c>
+      <c r="V21" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O22" s="3">
+        <v>2</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9">
+        <v>4</v>
+      </c>
+      <c r="V22" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M23" s="3">
+        <v>1</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>2</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="9">
+        <v>4</v>
+      </c>
+      <c r="V23" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O24" s="3">
+        <v>2</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="9">
+        <v>4</v>
+      </c>
+      <c r="V24" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M25" s="3">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O25" s="3">
+        <v>2</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="9">
+        <v>4</v>
+      </c>
+      <c r="V25" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M26" s="3">
+        <v>1</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>2</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="9">
+        <v>4</v>
+      </c>
+      <c r="V26" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="B27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M27" s="3">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O27" s="3">
+        <v>2</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="9">
+        <v>4</v>
+      </c>
+      <c r="V27" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="B28" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>2</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="9">
+        <v>4</v>
+      </c>
+      <c r="V28" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22">
+      <c r="B29" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O29" s="3">
+        <v>2</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>2</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="9">
+        <v>4</v>
+      </c>
+      <c r="V29" s="20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22">
+      <c r="B30" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M30" s="3">
+        <v>1</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="9">
+        <v>3</v>
+      </c>
+      <c r="V30" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22">
+      <c r="B31" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="3">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O31" s="3">
+        <v>2</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="9">
+        <v>3</v>
+      </c>
+      <c r="V31" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22">
+      <c r="B32" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O32" s="3">
+        <v>2</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="9">
+        <v>3</v>
+      </c>
+      <c r="V32" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22">
+      <c r="B33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="3">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="9">
+        <v>3</v>
+      </c>
+      <c r="V33" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22">
+      <c r="B34" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>2</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="9">
+        <v>3</v>
+      </c>
+      <c r="V34" s="20">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22">
+      <c r="B35" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M35" s="3">
+        <v>1</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S35" s="3">
+        <v>2</v>
+      </c>
+      <c r="T35" s="9">
+        <v>3</v>
+      </c>
+      <c r="V35" s="20">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22">
+      <c r="B36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O36" s="3">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S36" s="3">
+        <v>0</v>
+      </c>
+      <c r="T36" s="9">
+        <v>2</v>
+      </c>
+      <c r="V36" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22">
+      <c r="B37" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="3">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M37" s="3">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O37" s="3">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S37" s="3">
+        <v>0</v>
+      </c>
+      <c r="T37" s="9">
+        <v>2</v>
+      </c>
+      <c r="V37" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22">
+      <c r="B38" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O38" s="3">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S38" s="3">
+        <v>2</v>
+      </c>
+      <c r="T38" s="9">
+        <v>2</v>
+      </c>
+      <c r="V38" s="20">
+        <f t="shared" ref="V38:V58" si="1">COUNTIF(D38:S38,"---")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22">
+      <c r="B39" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="3">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="3">
+        <v>1</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O39" s="3">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S39" s="3">
+        <v>0</v>
+      </c>
+      <c r="T39" s="9">
+        <v>2</v>
+      </c>
+      <c r="V39" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:24">
-      <c r="B9" s="6"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X9" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22">
+      <c r="B40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M40" s="3">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O40" s="3">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S40" s="3">
+        <v>0</v>
+      </c>
+      <c r="T40" s="9">
+        <v>1</v>
+      </c>
+      <c r="V40" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:24">
-      <c r="B10" s="6"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="43">
+    <row r="41" spans="2:22">
+      <c r="B41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="11"/>
+      <c r="D41" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="9">
+        <v>1</v>
+      </c>
+      <c r="V41" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:24">
-      <c r="B11" s="6"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22">
+      <c r="B42" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="9">
+        <v>1</v>
+      </c>
+      <c r="V42" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:24">
-      <c r="B12" s="6"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22">
+      <c r="B43" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="9">
+        <v>1</v>
+      </c>
+      <c r="V43" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:24">
-      <c r="B13" s="6"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X13" s="43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22">
+      <c r="B44" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="9">
+        <v>1</v>
+      </c>
+      <c r="V44" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:24">
-      <c r="B14" s="6"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22">
+      <c r="B45" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="9">
+        <v>1</v>
+      </c>
+      <c r="V45" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:24">
-      <c r="B15" s="6"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22">
+      <c r="B46" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M46" s="3">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="9">
+        <v>1</v>
+      </c>
+      <c r="V46" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:24">
-      <c r="B16" s="6"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22">
+      <c r="B47" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M47" s="3">
+        <v>1</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="9">
+        <v>1</v>
+      </c>
+      <c r="V47" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24">
-      <c r="B17" s="6"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22">
+      <c r="B48" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M48" s="3">
+        <v>1</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="9">
+        <v>1</v>
+      </c>
+      <c r="V48" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:24">
-      <c r="B18" s="6"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X18" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="2:22">
+      <c r="B49" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="9">
+        <v>0</v>
+      </c>
+      <c r="V49" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:24">
-      <c r="B19" s="6"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22">
+      <c r="B50" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0</v>
+      </c>
+      <c r="V50" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:24">
-      <c r="B20" s="6"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="2:22">
+      <c r="B51" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
+      <c r="V51" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:24">
-      <c r="B21" s="6"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="2:22">
+      <c r="B52" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="9">
+        <v>0</v>
+      </c>
+      <c r="V52" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24">
-      <c r="B22" s="6"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="2:22">
+      <c r="B53" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="9">
+        <v>0</v>
+      </c>
+      <c r="V53" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:24">
-      <c r="B23" s="6"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X23" s="43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="2:22">
+      <c r="B54" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G54" s="3">
+        <v>0</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="K54" s="3">
+        <v>0</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O54" s="3">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S54" s="3">
+        <v>0</v>
+      </c>
+      <c r="T54" s="9">
+        <v>0</v>
+      </c>
+      <c r="V54" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:24">
-      <c r="B24" s="6"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="2:22">
+      <c r="B55" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M55" s="3">
+        <v>0</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O55" s="3">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S55" s="3">
+        <v>0</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0</v>
+      </c>
+      <c r="V55" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:24">
-      <c r="B25" s="6"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="2:22">
+      <c r="B56" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K56" s="3">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M56" s="3">
+        <v>0</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O56" s="3">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S56" s="3">
+        <v>0</v>
+      </c>
+      <c r="T56" s="9">
+        <v>0</v>
+      </c>
+      <c r="V56" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:24">
-      <c r="B26" s="6"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="2:22">
+      <c r="B57" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="9">
+        <v>0</v>
+      </c>
+      <c r="V57" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:24">
-      <c r="B27" s="6"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="2:22" ht="15" thickBot="1">
+      <c r="B58" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E58" s="5">
+        <v>0</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G58" s="5">
+        <v>0</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="I58" s="5">
+        <v>0</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="L58" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="M58" s="5">
+        <v>0</v>
+      </c>
+      <c r="N58" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="O58" s="5">
+        <v>0</v>
+      </c>
+      <c r="P58" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>0</v>
+      </c>
+      <c r="R58" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="S58" s="5">
+        <v>0</v>
+      </c>
+      <c r="T58" s="10">
+        <v>0</v>
+      </c>
+      <c r="V58" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:24">
-      <c r="B28" s="6"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:24">
-      <c r="B29" s="6"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X29" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:24">
-      <c r="B30" s="6"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X30" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:24">
-      <c r="B31" s="6"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:24">
-      <c r="B32" s="6"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24">
-      <c r="B33" s="6"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X33" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24">
-      <c r="B34" s="6"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X34" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:24">
-      <c r="B35" s="6"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="2"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X35" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:24">
-      <c r="B36" s="6"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24">
-      <c r="B37" s="6"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="2"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X37" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:24">
-      <c r="B38" s="6"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X38" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24">
-      <c r="B39" s="6"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="2"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X39" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:24">
-      <c r="B40" s="6"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="2"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X40" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:24">
-      <c r="B41" s="6"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="2"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X41" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24">
-      <c r="B42" s="6"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="2"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X42" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:24">
-      <c r="B43" s="6"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="2"/>
-      <c r="U43" s="3"/>
-      <c r="V43" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X43" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:24">
-      <c r="B44" s="6"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="3"/>
-      <c r="T44" s="2"/>
-      <c r="U44" s="3"/>
-      <c r="V44" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X44" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:24">
-      <c r="B45" s="6"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="2"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X45" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:24">
-      <c r="B46" s="6"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="3"/>
-      <c r="V46" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X46" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:24">
-      <c r="B47" s="6"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="2"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X47" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:24">
-      <c r="B48" s="6"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="2"/>
-      <c r="U48" s="3"/>
-      <c r="V48" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X48" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:24">
-      <c r="B49" s="6"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="2"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X49" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:24">
-      <c r="B50" s="6"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="2"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X50" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:24">
-      <c r="B51" s="6"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X51" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:24">
-      <c r="B52" s="6"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="2"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X52" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:24">
-      <c r="B53" s="6"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="3"/>
-      <c r="V53" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X53" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:24">
-      <c r="B54" s="6"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="2"/>
-      <c r="Q54" s="3"/>
-      <c r="R54" s="2"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="2"/>
-      <c r="U54" s="3"/>
-      <c r="V54" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X54" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:24">
-      <c r="B55" s="6"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="2"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="2"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X55" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:24">
-      <c r="B56" s="6"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="3"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="3"/>
-      <c r="T56" s="2"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X56" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:24">
-      <c r="B57" s="6"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="2"/>
-      <c r="U57" s="3"/>
-      <c r="V57" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X57" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:24">
-      <c r="B58" s="6"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" s="3"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="3"/>
-      <c r="T58" s="2"/>
-      <c r="U58" s="3"/>
-      <c r="V58" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X58" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:24">
-      <c r="B59" s="6"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="2"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X59" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:24">
-      <c r="B60" s="6"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="2"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="2"/>
-      <c r="U60" s="3"/>
-      <c r="V60" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X60" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:24">
-      <c r="B61" s="6"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="2"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="2"/>
-      <c r="Q61" s="3"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="3"/>
-      <c r="T61" s="2"/>
-      <c r="U61" s="3"/>
-      <c r="V61" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X61" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:24" ht="15" thickBot="1">
-      <c r="B62" s="7"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="5"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="5"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="5"/>
-      <c r="V62" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X62" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="29">
     <mergeCell ref="V3:V5"/>
-    <mergeCell ref="X3:X5"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
@@ -8530,79 +9690,72 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B2:T2"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P5:Q5"/>
     <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
     <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="T5:U5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
+    <mergeCell ref="T3:T5"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6:C196 T6:T196">
+    <cfRule type="expression" dxfId="10" priority="12">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="23" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>$D$5</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576 G1:G1048576 I1:I1048576 K1:K1048576 M1:M1048576 O1:O1048576 Q1:Q1048576 S1:S1048576">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>$F$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>$H$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>$J$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>$L$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>$N$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:P1048576">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>$P$5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R1048576">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>$R$5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T1:T1048576">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
-      <formula>$T$5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576 G1:G1048576 I1:I1048576 K1:K1048576 M1:M1048576 O1:O1048576 Q1:Q1048576 S1:S1048576 U1:U1048576">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:C200 P6:P200">
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
